--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EB50B1-726F-4A6B-AD50-837BE78A3E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D963C90-44E0-4F76-AEBB-C4F34526B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t>nome</t>
   </si>
@@ -1080,13 +1080,55 @@
   </si>
   <si>
     <t>c76a9e1a-a4af-4493-a8e2-18b5d0c36866</t>
+  </si>
+  <si>
+    <t>ALESSANDRA OLIVEIRA DE SOUSA</t>
+  </si>
+  <si>
+    <t>0608f354-affd-4e3c-ace3-30bdca2bb752</t>
+  </si>
+  <si>
+    <t>ANA LUCIA DE PAULA</t>
+  </si>
+  <si>
+    <t>b8e7415a-6ac1-4d70-92bf-184363e2b21d</t>
+  </si>
+  <si>
+    <t>DANIELA APARECIDA DE SOUZA</t>
+  </si>
+  <si>
+    <t>512c131c-953a-4f23-a2c6-23e4dda61ae9</t>
+  </si>
+  <si>
+    <t>GLAUCIA VIDA SOUZA LIMA</t>
+  </si>
+  <si>
+    <t>3c7b4f5f-7e9f-487c-a1c7-486e5371bad5</t>
+  </si>
+  <si>
+    <t>LAIANE VITORIA DA SILVA</t>
+  </si>
+  <si>
+    <t>5af59375-c6a6-421d-85bd-815ffb4b86fc</t>
+  </si>
+  <si>
+    <t>MARCELA LUISA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>d8064051-ae4c-4cbd-acb0-497614c0736a</t>
+  </si>
+  <si>
+    <t>ZENAIDE ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>68a72cce-a190-423f-9e45-ffff46287230</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1119,24 +1161,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF268BD2"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color rgb="FF6C71C4"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color rgb="FF002B36"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF5A5C5E"/>
       <name val="Arial"/>
@@ -1151,6 +1175,12 @@
     <font>
       <sz val="8"/>
       <color rgb="FF002B36"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5A5C5E"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1175,7 +1205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1190,22 +1220,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3433,7 +3457,7 @@
       <c r="A171">
         <v>5311</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="5" t="s">
         <v>341</v>
       </c>
       <c r="C171" t="s">
@@ -3444,7 +3468,7 @@
       <c r="A172">
         <v>5317</v>
       </c>
-      <c r="B172" s="9" t="s">
+      <c r="B172" s="6" t="s">
         <v>343</v>
       </c>
       <c r="C172" t="s">
@@ -3455,7 +3479,7 @@
       <c r="A173">
         <v>5306</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B173" s="7" t="s">
         <v>345</v>
       </c>
       <c r="C173" t="s">
@@ -3463,25 +3487,81 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B174" s="5"/>
+      <c r="A174">
+        <v>5323</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C174" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B175" s="6"/>
+      <c r="A175">
+        <v>5322</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C175" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B176" s="7"/>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B177" s="5"/>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B178" s="6"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B179" s="7"/>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B180" s="5"/>
+      <c r="A176">
+        <v>5315</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C176" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A177">
+        <v>5310</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C177" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A178">
+        <v>5325</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C178" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A179">
+        <v>5326</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="C179" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A180">
+        <v>5324</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C180" t="s">
+        <v>360</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C164" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D963C90-44E0-4F76-AEBB-C4F34526B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22039AAD-8E1B-47F5-91DE-1629861DF181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t>nome</t>
   </si>
@@ -1122,13 +1122,19 @@
   </si>
   <si>
     <t>68a72cce-a190-423f-9e45-ffff46287230</t>
+  </si>
+  <si>
+    <t>JESSICA SEGGER DA COSTA</t>
+  </si>
+  <si>
+    <t>5377f067-3d21-497a-83bf-acf7d64f9f24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1184,6 +1190,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5A5C5E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1205,7 +1217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1229,6 +1241,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1576,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="39.19921875" bestFit="1" customWidth="1"/>
@@ -3561,6 +3576,17 @@
       </c>
       <c r="C180" t="s">
         <v>360</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A181">
+        <v>5328</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C181" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22039AAD-8E1B-47F5-91DE-1629861DF181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90760484-CCF7-47D6-B778-0E6A08C221BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <si>
     <t>nome</t>
   </si>
@@ -1128,13 +1128,25 @@
   </si>
   <si>
     <t>5377f067-3d21-497a-83bf-acf7d64f9f24</t>
+  </si>
+  <si>
+    <t>86c1026e-8132-42b1-a4ce-c18df61758a3</t>
+  </si>
+  <si>
+    <t>ANGELA NOVAIS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MARIA ELILDA SILVA DE SOUSA</t>
+  </si>
+  <si>
+    <t>487cb177-fe8f-461c-a57e-621912586065</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1196,6 +1208,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5A5C5E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1217,7 +1235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1244,6 +1262,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1591,7 +1612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="39.19921875" bestFit="1" customWidth="1"/>
@@ -3587,6 +3608,28 @@
       </c>
       <c r="C181" t="s">
         <v>362</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A182">
+        <v>5327</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A183">
+        <v>5329</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C183" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTEGRADOR_EQUIPPE\EXCEL AHGORA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90760484-CCF7-47D6-B778-0E6A08C221BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E667443-83FD-4F09-B710-58CFE25BCBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
   <si>
     <t>nome</t>
   </si>
@@ -1140,6 +1140,24 @@
   </si>
   <si>
     <t>487cb177-fe8f-461c-a57e-621912586065</t>
+  </si>
+  <si>
+    <t>ANA PAULA MARINHO</t>
+  </si>
+  <si>
+    <t>aa704214-94e8-4698-ac21-9f4fdb948328</t>
+  </si>
+  <si>
+    <t>LETICIA CANDIDO SCOTT MEFFE</t>
+  </si>
+  <si>
+    <t>JAINA PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>3a34034e-8bfd-4409-a093-2eab15afe597</t>
+  </si>
+  <si>
+    <t>dcccca14-cc5a-49b4-b544-95b42acc13c8</t>
   </si>
 </sst>
 </file>
@@ -1612,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="39.19921875" bestFit="1" customWidth="1"/>
@@ -3630,6 +3648,39 @@
       </c>
       <c r="C183" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A184">
+        <v>5334</v>
+      </c>
+      <c r="B184" t="s">
+        <v>367</v>
+      </c>
+      <c r="C184" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A185">
+        <v>5330</v>
+      </c>
+      <c r="B185" t="s">
+        <v>369</v>
+      </c>
+      <c r="C185" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A186">
+        <v>5333</v>
+      </c>
+      <c r="B186" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INTEGRADOR_EQUIPPE\EXCEL AHGORA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E667443-83FD-4F09-B710-58CFE25BCBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B1326E-BA1B-48E7-B17E-8090036BBABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
   <si>
     <t>nome</t>
   </si>
@@ -1158,6 +1158,12 @@
   </si>
   <si>
     <t>dcccca14-cc5a-49b4-b544-95b42acc13c8</t>
+  </si>
+  <si>
+    <t>ANA CAROLINA SOUSA VIEIRA</t>
+  </si>
+  <si>
+    <t>fc3d4730-af0b-4258-945c-b5af9a7ceca4</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="39.19921875" bestFit="1" customWidth="1"/>
@@ -3681,6 +3687,17 @@
       </c>
       <c r="C186" t="s">
         <v>371</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A187">
+        <v>5335</v>
+      </c>
+      <c r="B187" t="s">
+        <v>373</v>
+      </c>
+      <c r="C187" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B1326E-BA1B-48E7-B17E-8090036BBABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204545F5-BB1F-4C93-90BA-CC379178F1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
+    <workbookView xWindow="3909" yWindow="3909" windowWidth="18514" windowHeight="11014" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
   <si>
     <t>nome</t>
   </si>
@@ -1164,6 +1164,72 @@
   </si>
   <si>
     <t>fc3d4730-af0b-4258-945c-b5af9a7ceca4</t>
+  </si>
+  <si>
+    <t>BRUNA SANTOS FERREIRA</t>
+  </si>
+  <si>
+    <t>51848aa8-ff8e-42fb-88d2-1a330802ce87</t>
+  </si>
+  <si>
+    <t>JOSENILTON JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>f7401f6f-ef71-4a2c-b8c0-92ea7a80d60a</t>
+  </si>
+  <si>
+    <t>LUANA CARVALHO PAULINO</t>
+  </si>
+  <si>
+    <t>11a1a148-0d98-43cb-91f4-e70a576b3ab4</t>
+  </si>
+  <si>
+    <t>LUCIANA FERREIRA BRITO</t>
+  </si>
+  <si>
+    <t>7609ed86-1893-4db7-914d-d0d7c755370b</t>
+  </si>
+  <si>
+    <t>PATRICIA PEDRO BATISTA DA SILVA</t>
+  </si>
+  <si>
+    <t>c3251f15-7c40-4be1-bdd0-529cbadb874c</t>
+  </si>
+  <si>
+    <t>RAFAELA SOUZA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>c8d95c8d-3501-4e78-9e63-3724ab96a79c</t>
+  </si>
+  <si>
+    <t>VITORIA OLIVEIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>26d0378b-f16f-4bd8-a1d0-8d14ea9b2f10</t>
+  </si>
+  <si>
+    <t>ALINE CRISTINA SOARES</t>
+  </si>
+  <si>
+    <t>1a2b4fb1-50e4-4011-b54a-d7955e13e958</t>
+  </si>
+  <si>
+    <t>DAYANA ALVES DE MOURA SALES</t>
+  </si>
+  <si>
+    <t>69b2ac34-b7d4-47fc-b8fa-0e1ca40cf789</t>
+  </si>
+  <si>
+    <t>ERICKSON COSMO RODRIGUES</t>
+  </si>
+  <si>
+    <t>ec91bcf5-6599-4a50-a182-e1a312db50f3</t>
+  </si>
+  <si>
+    <t>MARTA BRITO NERY DUARTE</t>
+  </si>
+  <si>
+    <t>34f7fd0e-ad2b-4eef-be97-1891ad7c4fe2</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1361,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1636,14 +1712,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C187"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C198"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="39.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1654,7 +1730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1665,7 +1741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>224</v>
       </c>
@@ -1676,7 +1752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>236</v>
       </c>
@@ -1687,7 +1763,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1221</v>
       </c>
@@ -1698,7 +1774,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1464</v>
       </c>
@@ -1709,7 +1785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1499</v>
       </c>
@@ -1720,7 +1796,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2063</v>
       </c>
@@ -1731,7 +1807,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2086</v>
       </c>
@@ -1742,7 +1818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>2638</v>
       </c>
@@ -1753,7 +1829,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2916</v>
       </c>
@@ -1764,7 +1840,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>3014</v>
       </c>
@@ -1775,7 +1851,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>3230</v>
       </c>
@@ -1786,7 +1862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>3358</v>
       </c>
@@ -1797,7 +1873,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>3435</v>
       </c>
@@ -1808,7 +1884,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>3528</v>
       </c>
@@ -1819,7 +1895,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>3688</v>
       </c>
@@ -1830,7 +1906,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>3709</v>
       </c>
@@ -1841,7 +1917,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3727</v>
       </c>
@@ -1852,7 +1928,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3729</v>
       </c>
@@ -1863,7 +1939,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3811</v>
       </c>
@@ -1874,7 +1950,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3874</v>
       </c>
@@ -1885,7 +1961,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3908</v>
       </c>
@@ -1896,7 +1972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3951</v>
       </c>
@@ -1907,7 +1983,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>4007</v>
       </c>
@@ -1918,7 +1994,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4031</v>
       </c>
@@ -1929,7 +2005,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4039</v>
       </c>
@@ -1940,7 +2016,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4111</v>
       </c>
@@ -1951,7 +2027,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4262</v>
       </c>
@@ -1962,7 +2038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4300</v>
       </c>
@@ -1973,7 +2049,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4333</v>
       </c>
@@ -1984,7 +2060,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>4340</v>
       </c>
@@ -1995,7 +2071,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>4369</v>
       </c>
@@ -2006,7 +2082,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>4390</v>
       </c>
@@ -2017,7 +2093,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>4433</v>
       </c>
@@ -2028,7 +2104,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>4464</v>
       </c>
@@ -2039,7 +2115,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>4476</v>
       </c>
@@ -2050,7 +2126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>4509</v>
       </c>
@@ -2061,7 +2137,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>4530</v>
       </c>
@@ -2072,7 +2148,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>4558</v>
       </c>
@@ -2083,7 +2159,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>4561</v>
       </c>
@@ -2094,7 +2170,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>4563</v>
       </c>
@@ -2105,7 +2181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>4581</v>
       </c>
@@ -2116,7 +2192,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>4618</v>
       </c>
@@ -2127,7 +2203,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>4640</v>
       </c>
@@ -2138,7 +2214,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>4668</v>
       </c>
@@ -2149,7 +2225,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>4683</v>
       </c>
@@ -2160,7 +2236,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>4703</v>
       </c>
@@ -2171,7 +2247,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>4734</v>
       </c>
@@ -2182,7 +2258,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4739</v>
       </c>
@@ -2193,7 +2269,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>4751</v>
       </c>
@@ -2204,7 +2280,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>4752</v>
       </c>
@@ -2215,7 +2291,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>4794</v>
       </c>
@@ -2226,7 +2302,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>4806</v>
       </c>
@@ -2237,7 +2313,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>4816</v>
       </c>
@@ -2248,7 +2324,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>4820</v>
       </c>
@@ -2259,7 +2335,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>4837</v>
       </c>
@@ -2270,7 +2346,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4838</v>
       </c>
@@ -2281,7 +2357,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4841</v>
       </c>
@@ -2292,7 +2368,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4858</v>
       </c>
@@ -2303,7 +2379,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4861</v>
       </c>
@@ -2314,7 +2390,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4863</v>
       </c>
@@ -2325,7 +2401,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4886</v>
       </c>
@@ -2336,7 +2412,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4895</v>
       </c>
@@ -2347,7 +2423,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4896</v>
       </c>
@@ -2358,7 +2434,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4902</v>
       </c>
@@ -2369,7 +2445,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4904</v>
       </c>
@@ -2380,7 +2456,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>4906</v>
       </c>
@@ -2391,7 +2467,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>4908</v>
       </c>
@@ -2402,7 +2478,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>4925</v>
       </c>
@@ -2413,7 +2489,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>4935</v>
       </c>
@@ -2424,7 +2500,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>4945</v>
       </c>
@@ -2435,7 +2511,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>4950</v>
       </c>
@@ -2446,7 +2522,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>4957</v>
       </c>
@@ -2457,7 +2533,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>4972</v>
       </c>
@@ -2468,7 +2544,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>4981</v>
       </c>
@@ -2479,7 +2555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>4994</v>
       </c>
@@ -2490,7 +2566,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>5008</v>
       </c>
@@ -2501,7 +2577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>5019</v>
       </c>
@@ -2512,7 +2588,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>5028</v>
       </c>
@@ -2523,7 +2599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>5038</v>
       </c>
@@ -2534,7 +2610,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>5043</v>
       </c>
@@ -2545,7 +2621,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>5046</v>
       </c>
@@ -2556,7 +2632,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>5051</v>
       </c>
@@ -2567,7 +2643,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>5054</v>
       </c>
@@ -2578,7 +2654,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>5055</v>
       </c>
@@ -2589,7 +2665,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>5064</v>
       </c>
@@ -2600,7 +2676,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>5078</v>
       </c>
@@ -2611,7 +2687,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>5082</v>
       </c>
@@ -2622,7 +2698,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>5084</v>
       </c>
@@ -2633,7 +2709,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>5102</v>
       </c>
@@ -2644,7 +2720,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>5108</v>
       </c>
@@ -2655,7 +2731,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>5113</v>
       </c>
@@ -2666,7 +2742,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>5114</v>
       </c>
@@ -2677,7 +2753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>5117</v>
       </c>
@@ -2688,7 +2764,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>5118</v>
       </c>
@@ -2699,7 +2775,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>5123</v>
       </c>
@@ -2710,7 +2786,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>5127</v>
       </c>
@@ -2721,7 +2797,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>5129</v>
       </c>
@@ -2732,7 +2808,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>5130</v>
       </c>
@@ -2743,7 +2819,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>5133</v>
       </c>
@@ -2754,7 +2830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>5137</v>
       </c>
@@ -2765,7 +2841,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>5138</v>
       </c>
@@ -2776,7 +2852,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>5139</v>
       </c>
@@ -2787,7 +2863,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>5144</v>
       </c>
@@ -2798,7 +2874,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>5150</v>
       </c>
@@ -2809,7 +2885,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>5151</v>
       </c>
@@ -2820,7 +2896,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>5155</v>
       </c>
@@ -2831,7 +2907,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>5157</v>
       </c>
@@ -2842,7 +2918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>5160</v>
       </c>
@@ -2853,7 +2929,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>5167</v>
       </c>
@@ -2864,7 +2940,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>5170</v>
       </c>
@@ -2875,7 +2951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>5175</v>
       </c>
@@ -2886,7 +2962,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>5176</v>
       </c>
@@ -2897,7 +2973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>5177</v>
       </c>
@@ -2908,7 +2984,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>5181</v>
       </c>
@@ -2919,7 +2995,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>5182</v>
       </c>
@@ -2930,7 +3006,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>5197</v>
       </c>
@@ -2941,7 +3017,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>5201</v>
       </c>
@@ -2952,7 +3028,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>5203</v>
       </c>
@@ -2963,7 +3039,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>5204</v>
       </c>
@@ -2974,7 +3050,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>5208</v>
       </c>
@@ -2985,7 +3061,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>5218</v>
       </c>
@@ -2996,7 +3072,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>5224</v>
       </c>
@@ -3007,7 +3083,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>5225</v>
       </c>
@@ -3018,7 +3094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>5227</v>
       </c>
@@ -3029,7 +3105,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>5232</v>
       </c>
@@ -3040,7 +3116,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>5235</v>
       </c>
@@ -3051,7 +3127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>5236</v>
       </c>
@@ -3062,7 +3138,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>5238</v>
       </c>
@@ -3073,7 +3149,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>5239</v>
       </c>
@@ -3084,7 +3160,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>5242</v>
       </c>
@@ -3095,7 +3171,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>5247</v>
       </c>
@@ -3106,7 +3182,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>5251</v>
       </c>
@@ -3117,7 +3193,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>5252</v>
       </c>
@@ -3128,7 +3204,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>5254</v>
       </c>
@@ -3139,7 +3215,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>5255</v>
       </c>
@@ -3150,7 +3226,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>5256</v>
       </c>
@@ -3161,7 +3237,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>5257</v>
       </c>
@@ -3172,7 +3248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>5259</v>
       </c>
@@ -3183,7 +3259,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>5260</v>
       </c>
@@ -3194,7 +3270,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>5262</v>
       </c>
@@ -3205,7 +3281,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>5263</v>
       </c>
@@ -3216,7 +3292,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>5265</v>
       </c>
@@ -3227,7 +3303,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>5266</v>
       </c>
@@ -3238,7 +3314,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>5268</v>
       </c>
@@ -3249,7 +3325,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>5272</v>
       </c>
@@ -3260,7 +3336,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>5273</v>
       </c>
@@ -3271,7 +3347,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>5274</v>
       </c>
@@ -3282,7 +3358,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>5275</v>
       </c>
@@ -3293,7 +3369,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>5277</v>
       </c>
@@ -3304,7 +3380,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>5278</v>
       </c>
@@ -3315,7 +3391,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>5279</v>
       </c>
@@ -3326,7 +3402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>5280</v>
       </c>
@@ -3337,7 +3413,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>5281</v>
       </c>
@@ -3348,7 +3424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>5282</v>
       </c>
@@ -3359,7 +3435,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>5284</v>
       </c>
@@ -3370,7 +3446,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>5286</v>
       </c>
@@ -3381,7 +3457,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>5287</v>
       </c>
@@ -3392,7 +3468,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>5288</v>
       </c>
@@ -3403,7 +3479,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>5289</v>
       </c>
@@ -3414,7 +3490,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>5290</v>
       </c>
@@ -3425,7 +3501,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>5292</v>
       </c>
@@ -3436,7 +3512,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>5293</v>
       </c>
@@ -3447,7 +3523,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>5283</v>
       </c>
@@ -3458,7 +3534,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>5301</v>
       </c>
@@ -3469,7 +3545,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>5302</v>
       </c>
@@ -3480,7 +3556,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>5303</v>
       </c>
@@ -3491,7 +3567,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>5298</v>
       </c>
@@ -3502,7 +3578,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>5295</v>
       </c>
@@ -3513,7 +3589,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>5311</v>
       </c>
@@ -3524,7 +3600,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>5317</v>
       </c>
@@ -3535,7 +3611,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>5306</v>
       </c>
@@ -3546,7 +3622,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>5323</v>
       </c>
@@ -3557,7 +3633,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>5322</v>
       </c>
@@ -3568,7 +3644,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>5315</v>
       </c>
@@ -3579,7 +3655,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>5310</v>
       </c>
@@ -3590,7 +3666,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>5325</v>
       </c>
@@ -3601,7 +3677,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>5326</v>
       </c>
@@ -3612,7 +3688,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>5324</v>
       </c>
@@ -3623,7 +3699,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>5328</v>
       </c>
@@ -3634,7 +3710,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>5327</v>
       </c>
@@ -3645,7 +3721,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>5329</v>
       </c>
@@ -3656,7 +3732,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>5334</v>
       </c>
@@ -3667,7 +3743,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>5330</v>
       </c>
@@ -3678,7 +3754,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>5333</v>
       </c>
@@ -3689,7 +3765,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>5335</v>
       </c>
@@ -3698,6 +3774,127 @@
       </c>
       <c r="C187" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A188">
+        <v>5338</v>
+      </c>
+      <c r="B188" t="s">
+        <v>375</v>
+      </c>
+      <c r="C188" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A189">
+        <v>5304</v>
+      </c>
+      <c r="B189" t="s">
+        <v>377</v>
+      </c>
+      <c r="C189" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A190">
+        <v>5307</v>
+      </c>
+      <c r="B190" t="s">
+        <v>379</v>
+      </c>
+      <c r="C190" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A191">
+        <v>5332</v>
+      </c>
+      <c r="B191" t="s">
+        <v>381</v>
+      </c>
+      <c r="C191" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A192">
+        <v>5297</v>
+      </c>
+      <c r="B192" t="s">
+        <v>383</v>
+      </c>
+      <c r="C192" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A193">
+        <v>5314</v>
+      </c>
+      <c r="B193" t="s">
+        <v>385</v>
+      </c>
+      <c r="C193" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A194">
+        <v>5337</v>
+      </c>
+      <c r="B194" t="s">
+        <v>387</v>
+      </c>
+      <c r="C194" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A195">
+        <v>5308</v>
+      </c>
+      <c r="B195" t="s">
+        <v>389</v>
+      </c>
+      <c r="C195" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A196">
+        <v>5305</v>
+      </c>
+      <c r="B196" t="s">
+        <v>391</v>
+      </c>
+      <c r="C196" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A197">
+        <v>5336</v>
+      </c>
+      <c r="B197" t="s">
+        <v>393</v>
+      </c>
+      <c r="C197" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A198">
+        <v>5319</v>
+      </c>
+      <c r="B198" t="s">
+        <v>395</v>
+      </c>
+      <c r="C198" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -3705,8 +3902,11 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C157">
     <sortCondition ref="A139:A157"/>
   </sortState>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204545F5-BB1F-4C93-90BA-CC379178F1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC8CDF00-7695-410C-AF27-8C7DAFFDE44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3909" yWindow="3909" windowWidth="18514" windowHeight="11014" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="399">
   <si>
     <t>nome</t>
   </si>
@@ -1230,6 +1230,12 @@
   </si>
   <si>
     <t>34f7fd0e-ad2b-4eef-be97-1891ad7c4fe2</t>
+  </si>
+  <si>
+    <t>CAMILA OLIVEIRA MATIAS</t>
+  </si>
+  <si>
+    <t>69c82728-6767-415d-a526-81f646f7ea66</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="39.23046875" bestFit="1" customWidth="1"/>
@@ -3895,6 +3901,17 @@
       </c>
       <c r="C198" t="s">
         <v>396</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A199">
+        <v>5341</v>
+      </c>
+      <c r="B199" t="s">
+        <v>397</v>
+      </c>
+      <c r="C199" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC8CDF00-7695-410C-AF27-8C7DAFFDE44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFF5524-9B51-4E94-9AF7-85098B57D2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
   <si>
     <t>nome</t>
   </si>
@@ -1236,6 +1236,12 @@
   </si>
   <si>
     <t>69c82728-6767-415d-a526-81f646f7ea66</t>
+  </si>
+  <si>
+    <t>DAPHNE LOUISE DA SILVA</t>
+  </si>
+  <si>
+    <t>7356470d-dd99-4fb9-868b-b626f5ff053e</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C199"/>
+  <dimension ref="A1:C200"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="39.23046875" bestFit="1" customWidth="1"/>
@@ -3912,6 +3918,17 @@
       </c>
       <c r="C199" t="s">
         <v>398</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A200">
+        <v>5342</v>
+      </c>
+      <c r="B200" t="s">
+        <v>399</v>
+      </c>
+      <c r="C200" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFF5524-9B51-4E94-9AF7-85098B57D2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98020F19-E4E7-408D-944F-94B7D6B1CD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t>nome</t>
   </si>
@@ -1242,6 +1242,12 @@
   </si>
   <si>
     <t>7356470d-dd99-4fb9-868b-b626f5ff053e</t>
+  </si>
+  <si>
+    <t>CICERA ROSA PEREIRA</t>
+  </si>
+  <si>
+    <t>c5d0c01d-3717-4dba-bf51-652813b22c8c</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26FDFC0-3A15-4C58-8EAD-DAE315CBFD7D}">
-  <dimension ref="A1:C200"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="39.23046875" bestFit="1" customWidth="1"/>
@@ -3929,6 +3935,22 @@
       </c>
       <c r="C200" t="s">
         <v>400</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A201">
+        <v>5343</v>
+      </c>
+      <c r="B201" t="s">
+        <v>401</v>
+      </c>
+      <c r="C201" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="217" spans="6:6" x14ac:dyDescent="0.4">
+      <c r="F217">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98020F19-E4E7-408D-944F-94B7D6B1CD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4831BCE9-2692-4E43-BB9B-412E418821ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
+    <workbookView xWindow="23543" yWindow="180" windowWidth="18517" windowHeight="10740" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>matricula</t>
   </si>
   <si>
-    <t>Coluna2</t>
-  </si>
-  <si>
     <t>FRANCISCA DALVANI DO NASCIMENTO LIMA</t>
   </si>
   <si>
@@ -1248,6 +1245,9 @@
   </si>
   <si>
     <t>c5d0c01d-3717-4dba-bf51-652813b22c8c</t>
+  </si>
+  <si>
+    <t>stakeholderid</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -1753,10 +1753,10 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -1764,10 +1764,10 @@
         <v>224</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -1775,10 +1775,10 @@
         <v>236</v>
       </c>
       <c r="B4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" t="s">
         <v>240</v>
-      </c>
-      <c r="C4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -1786,10 +1786,10 @@
         <v>1221</v>
       </c>
       <c r="B5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" t="s">
         <v>221</v>
-      </c>
-      <c r="C5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -1797,10 +1797,10 @@
         <v>1464</v>
       </c>
       <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
         <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -1808,10 +1808,10 @@
         <v>1499</v>
       </c>
       <c r="B7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" t="s">
         <v>251</v>
-      </c>
-      <c r="C7" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -1819,10 +1819,10 @@
         <v>2063</v>
       </c>
       <c r="B8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" t="s">
         <v>195</v>
-      </c>
-      <c r="C8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -1830,10 +1830,10 @@
         <v>2086</v>
       </c>
       <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
         <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -1841,10 +1841,10 @@
         <v>2638</v>
       </c>
       <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -1852,10 +1852,10 @@
         <v>2916</v>
       </c>
       <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
         <v>119</v>
-      </c>
-      <c r="C11" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -1863,10 +1863,10 @@
         <v>3014</v>
       </c>
       <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
         <v>135</v>
-      </c>
-      <c r="C12" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -1874,10 +1874,10 @@
         <v>3230</v>
       </c>
       <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
         <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
@@ -1885,10 +1885,10 @@
         <v>3358</v>
       </c>
       <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
         <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
@@ -1896,10 +1896,10 @@
         <v>3435</v>
       </c>
       <c r="B15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" t="s">
         <v>297</v>
-      </c>
-      <c r="C15" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
@@ -1907,10 +1907,10 @@
         <v>3528</v>
       </c>
       <c r="B16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" t="s">
         <v>201</v>
-      </c>
-      <c r="C16" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
@@ -1918,10 +1918,10 @@
         <v>3688</v>
       </c>
       <c r="B17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" t="s">
         <v>301</v>
-      </c>
-      <c r="C17" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
@@ -1929,10 +1929,10 @@
         <v>3709</v>
       </c>
       <c r="B18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" t="s">
         <v>141</v>
-      </c>
-      <c r="C18" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
@@ -1940,10 +1940,10 @@
         <v>3727</v>
       </c>
       <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
         <v>101</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -1951,10 +1951,10 @@
         <v>3729</v>
       </c>
       <c r="B20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s">
         <v>193</v>
-      </c>
-      <c r="C20" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -1962,10 +1962,10 @@
         <v>3811</v>
       </c>
       <c r="B21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" t="s">
         <v>227</v>
-      </c>
-      <c r="C21" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -1973,10 +1973,10 @@
         <v>3874</v>
       </c>
       <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s">
         <v>155</v>
-      </c>
-      <c r="C22" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
@@ -1984,10 +1984,10 @@
         <v>3908</v>
       </c>
       <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
         <v>55</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
@@ -1995,10 +1995,10 @@
         <v>3951</v>
       </c>
       <c r="B24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" t="s">
         <v>249</v>
-      </c>
-      <c r="C24" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
@@ -2006,10 +2006,10 @@
         <v>4007</v>
       </c>
       <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
         <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
@@ -2017,10 +2017,10 @@
         <v>4031</v>
       </c>
       <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
         <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -2028,10 +2028,10 @@
         <v>4039</v>
       </c>
       <c r="B27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" t="s">
         <v>219</v>
-      </c>
-      <c r="C27" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
@@ -2039,10 +2039,10 @@
         <v>4111</v>
       </c>
       <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
         <v>113</v>
-      </c>
-      <c r="C28" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
@@ -2050,10 +2050,10 @@
         <v>4262</v>
       </c>
       <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
         <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
@@ -2061,10 +2061,10 @@
         <v>4300</v>
       </c>
       <c r="B30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" t="s">
         <v>189</v>
-      </c>
-      <c r="C30" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
@@ -2072,10 +2072,10 @@
         <v>4333</v>
       </c>
       <c r="B31" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" t="s">
         <v>199</v>
-      </c>
-      <c r="C31" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
@@ -2083,10 +2083,10 @@
         <v>4340</v>
       </c>
       <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
@@ -2094,10 +2094,10 @@
         <v>4369</v>
       </c>
       <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
         <v>211</v>
-      </c>
-      <c r="C33" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
@@ -2105,10 +2105,10 @@
         <v>4390</v>
       </c>
       <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
         <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
@@ -2116,10 +2116,10 @@
         <v>4433</v>
       </c>
       <c r="B35" t="s">
+        <v>256</v>
+      </c>
+      <c r="C35" t="s">
         <v>257</v>
-      </c>
-      <c r="C35" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
@@ -2127,10 +2127,10 @@
         <v>4464</v>
       </c>
       <c r="B36" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" t="s">
         <v>171</v>
-      </c>
-      <c r="C36" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
@@ -2138,10 +2138,10 @@
         <v>4476</v>
       </c>
       <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
         <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
@@ -2149,10 +2149,10 @@
         <v>4509</v>
       </c>
       <c r="B38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" t="s">
         <v>131</v>
-      </c>
-      <c r="C38" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -2160,10 +2160,10 @@
         <v>4530</v>
       </c>
       <c r="B39" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" t="s">
         <v>265</v>
-      </c>
-      <c r="C39" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
@@ -2171,10 +2171,10 @@
         <v>4558</v>
       </c>
       <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
         <v>61</v>
-      </c>
-      <c r="C40" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
@@ -2182,10 +2182,10 @@
         <v>4561</v>
       </c>
       <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
         <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
@@ -2193,10 +2193,10 @@
         <v>4563</v>
       </c>
       <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
         <v>39</v>
-      </c>
-      <c r="C42" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
@@ -2204,10 +2204,10 @@
         <v>4581</v>
       </c>
       <c r="B43" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" t="s">
         <v>255</v>
-      </c>
-      <c r="C43" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
@@ -2215,10 +2215,10 @@
         <v>4618</v>
       </c>
       <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
         <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
@@ -2226,10 +2226,10 @@
         <v>4640</v>
       </c>
       <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
         <v>139</v>
-      </c>
-      <c r="C45" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
@@ -2237,10 +2237,10 @@
         <v>4668</v>
       </c>
       <c r="B46" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" t="s">
         <v>165</v>
-      </c>
-      <c r="C46" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
@@ -2248,10 +2248,10 @@
         <v>4683</v>
       </c>
       <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
         <v>117</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
@@ -2259,10 +2259,10 @@
         <v>4703</v>
       </c>
       <c r="B48" t="s">
+        <v>302</v>
+      </c>
+      <c r="C48" t="s">
         <v>303</v>
-      </c>
-      <c r="C48" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
@@ -2270,10 +2270,10 @@
         <v>4734</v>
       </c>
       <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
         <v>49</v>
-      </c>
-      <c r="C49" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
@@ -2281,10 +2281,10 @@
         <v>4739</v>
       </c>
       <c r="B50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" t="s">
         <v>127</v>
-      </c>
-      <c r="C50" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
@@ -2292,10 +2292,10 @@
         <v>4751</v>
       </c>
       <c r="B51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
         <v>238</v>
-      </c>
-      <c r="C51" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
@@ -2303,10 +2303,10 @@
         <v>4752</v>
       </c>
       <c r="B52" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" t="s">
         <v>283</v>
-      </c>
-      <c r="C52" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
@@ -2314,10 +2314,10 @@
         <v>4794</v>
       </c>
       <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s">
         <v>187</v>
-      </c>
-      <c r="C53" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
@@ -2325,10 +2325,10 @@
         <v>4806</v>
       </c>
       <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
         <v>67</v>
-      </c>
-      <c r="C54" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
@@ -2336,10 +2336,10 @@
         <v>4816</v>
       </c>
       <c r="B55" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" t="s">
         <v>267</v>
-      </c>
-      <c r="C55" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -2347,10 +2347,10 @@
         <v>4820</v>
       </c>
       <c r="B56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" t="s">
         <v>185</v>
-      </c>
-      <c r="C56" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
@@ -2358,10 +2358,10 @@
         <v>4837</v>
       </c>
       <c r="B57" t="s">
+        <v>212</v>
+      </c>
+      <c r="C57" t="s">
         <v>213</v>
-      </c>
-      <c r="C57" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
@@ -2369,10 +2369,10 @@
         <v>4838</v>
       </c>
       <c r="B58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" t="s">
         <v>207</v>
-      </c>
-      <c r="C58" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
@@ -2380,10 +2380,10 @@
         <v>4841</v>
       </c>
       <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" t="s">
         <v>217</v>
-      </c>
-      <c r="C59" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
@@ -2391,10 +2391,10 @@
         <v>4858</v>
       </c>
       <c r="B60" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" t="s">
         <v>177</v>
-      </c>
-      <c r="C60" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
@@ -2402,10 +2402,10 @@
         <v>4861</v>
       </c>
       <c r="B61" t="s">
+        <v>304</v>
+      </c>
+      <c r="C61" t="s">
         <v>305</v>
-      </c>
-      <c r="C61" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
@@ -2413,10 +2413,10 @@
         <v>4863</v>
       </c>
       <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" t="s">
         <v>47</v>
-      </c>
-      <c r="C62" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
@@ -2424,10 +2424,10 @@
         <v>4886</v>
       </c>
       <c r="B63" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" t="s">
         <v>157</v>
-      </c>
-      <c r="C63" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
@@ -2435,10 +2435,10 @@
         <v>4895</v>
       </c>
       <c r="B64" t="s">
+        <v>292</v>
+      </c>
+      <c r="C64" t="s">
         <v>293</v>
-      </c>
-      <c r="C64" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
@@ -2446,10 +2446,10 @@
         <v>4896</v>
       </c>
       <c r="B65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" t="s">
         <v>225</v>
-      </c>
-      <c r="C65" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
@@ -2457,10 +2457,10 @@
         <v>4902</v>
       </c>
       <c r="B66" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" t="s">
         <v>261</v>
-      </c>
-      <c r="C66" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
@@ -2468,10 +2468,10 @@
         <v>4904</v>
       </c>
       <c r="B67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" t="s">
         <v>151</v>
-      </c>
-      <c r="C67" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
@@ -2479,10 +2479,10 @@
         <v>4906</v>
       </c>
       <c r="B68" t="s">
+        <v>294</v>
+      </c>
+      <c r="C68" t="s">
         <v>295</v>
-      </c>
-      <c r="C68" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
@@ -2490,10 +2490,10 @@
         <v>4908</v>
       </c>
       <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="s">
         <v>75</v>
-      </c>
-      <c r="C69" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
@@ -2501,10 +2501,10 @@
         <v>4925</v>
       </c>
       <c r="B70" t="s">
+        <v>274</v>
+      </c>
+      <c r="C70" t="s">
         <v>275</v>
-      </c>
-      <c r="C70" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
@@ -2512,10 +2512,10 @@
         <v>4935</v>
       </c>
       <c r="B71" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s">
         <v>167</v>
-      </c>
-      <c r="C71" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
@@ -2523,10 +2523,10 @@
         <v>4945</v>
       </c>
       <c r="B72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" t="s">
         <v>197</v>
-      </c>
-      <c r="C72" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
@@ -2534,10 +2534,10 @@
         <v>4950</v>
       </c>
       <c r="B73" t="s">
+        <v>276</v>
+      </c>
+      <c r="C73" t="s">
         <v>277</v>
-      </c>
-      <c r="C73" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
@@ -2545,10 +2545,10 @@
         <v>4957</v>
       </c>
       <c r="B74" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" t="s">
         <v>105</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
@@ -2556,10 +2556,10 @@
         <v>4972</v>
       </c>
       <c r="B75" t="s">
+        <v>298</v>
+      </c>
+      <c r="C75" t="s">
         <v>299</v>
-      </c>
-      <c r="C75" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
@@ -2567,10 +2567,10 @@
         <v>4981</v>
       </c>
       <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" t="s">
         <v>15</v>
-      </c>
-      <c r="C76" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
@@ -2578,10 +2578,10 @@
         <v>4994</v>
       </c>
       <c r="B77" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" t="s">
         <v>203</v>
-      </c>
-      <c r="C77" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
@@ -2589,10 +2589,10 @@
         <v>5008</v>
       </c>
       <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
         <v>19</v>
-      </c>
-      <c r="C78" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
@@ -2600,10 +2600,10 @@
         <v>5019</v>
       </c>
       <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" t="s">
         <v>35</v>
-      </c>
-      <c r="C79" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
@@ -2611,10 +2611,10 @@
         <v>5028</v>
       </c>
       <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
         <v>21</v>
-      </c>
-      <c r="C80" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
@@ -2622,10 +2622,10 @@
         <v>5038</v>
       </c>
       <c r="B81" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" t="s">
         <v>169</v>
-      </c>
-      <c r="C81" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.4">
@@ -2633,10 +2633,10 @@
         <v>5043</v>
       </c>
       <c r="B82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" t="s">
         <v>91</v>
-      </c>
-      <c r="C82" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
@@ -2644,10 +2644,10 @@
         <v>5046</v>
       </c>
       <c r="B83" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" t="s">
         <v>69</v>
-      </c>
-      <c r="C83" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
@@ -2655,10 +2655,10 @@
         <v>5051</v>
       </c>
       <c r="B84" t="s">
+        <v>144</v>
+      </c>
+      <c r="C84" t="s">
         <v>145</v>
-      </c>
-      <c r="C84" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
@@ -2666,10 +2666,10 @@
         <v>5054</v>
       </c>
       <c r="B85" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" t="s">
         <v>215</v>
-      </c>
-      <c r="C85" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
@@ -2677,10 +2677,10 @@
         <v>5055</v>
       </c>
       <c r="B86" t="s">
+        <v>246</v>
+      </c>
+      <c r="C86" t="s">
         <v>247</v>
-      </c>
-      <c r="C86" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
@@ -2688,10 +2688,10 @@
         <v>5064</v>
       </c>
       <c r="B87" t="s">
+        <v>270</v>
+      </c>
+      <c r="C87" t="s">
         <v>271</v>
-      </c>
-      <c r="C87" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
@@ -2699,10 +2699,10 @@
         <v>5078</v>
       </c>
       <c r="B88" t="s">
+        <v>160</v>
+      </c>
+      <c r="C88" t="s">
         <v>161</v>
-      </c>
-      <c r="C88" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
@@ -2710,10 +2710,10 @@
         <v>5082</v>
       </c>
       <c r="B89" t="s">
+        <v>96</v>
+      </c>
+      <c r="C89" t="s">
         <v>97</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
@@ -2721,10 +2721,10 @@
         <v>5084</v>
       </c>
       <c r="B90" t="s">
+        <v>286</v>
+      </c>
+      <c r="C90" t="s">
         <v>287</v>
-      </c>
-      <c r="C90" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
@@ -2732,10 +2732,10 @@
         <v>5102</v>
       </c>
       <c r="B91" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" t="s">
         <v>111</v>
-      </c>
-      <c r="C91" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
@@ -2743,10 +2743,10 @@
         <v>5108</v>
       </c>
       <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" t="s">
         <v>159</v>
-      </c>
-      <c r="C92" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
@@ -2754,10 +2754,10 @@
         <v>5113</v>
       </c>
       <c r="B93" t="s">
+        <v>40</v>
+      </c>
+      <c r="C93" t="s">
         <v>41</v>
-      </c>
-      <c r="C93" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
@@ -2765,10 +2765,10 @@
         <v>5114</v>
       </c>
       <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" t="s">
         <v>25</v>
-      </c>
-      <c r="C94" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
@@ -2776,10 +2776,10 @@
         <v>5117</v>
       </c>
       <c r="B95" t="s">
+        <v>132</v>
+      </c>
+      <c r="C95" t="s">
         <v>133</v>
-      </c>
-      <c r="C95" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
@@ -2787,10 +2787,10 @@
         <v>5118</v>
       </c>
       <c r="B96" t="s">
+        <v>284</v>
+      </c>
+      <c r="C96" t="s">
         <v>285</v>
-      </c>
-      <c r="C96" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
@@ -2798,10 +2798,10 @@
         <v>5123</v>
       </c>
       <c r="B97" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97" t="s">
         <v>43</v>
-      </c>
-      <c r="C97" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
@@ -2809,10 +2809,10 @@
         <v>5127</v>
       </c>
       <c r="B98" t="s">
+        <v>262</v>
+      </c>
+      <c r="C98" t="s">
         <v>263</v>
-      </c>
-      <c r="C98" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
@@ -2820,10 +2820,10 @@
         <v>5129</v>
       </c>
       <c r="B99" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" t="s">
         <v>223</v>
-      </c>
-      <c r="C99" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
@@ -2831,10 +2831,10 @@
         <v>5130</v>
       </c>
       <c r="B100" t="s">
+        <v>106</v>
+      </c>
+      <c r="C100" t="s">
         <v>107</v>
-      </c>
-      <c r="C100" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
@@ -2842,10 +2842,10 @@
         <v>5133</v>
       </c>
       <c r="B101" t="s">
+        <v>64</v>
+      </c>
+      <c r="C101" t="s">
         <v>65</v>
-      </c>
-      <c r="C101" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
@@ -2853,10 +2853,10 @@
         <v>5137</v>
       </c>
       <c r="B102" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" t="s">
         <v>175</v>
-      </c>
-      <c r="C102" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
@@ -2864,10 +2864,10 @@
         <v>5138</v>
       </c>
       <c r="B103" t="s">
+        <v>235</v>
+      </c>
+      <c r="C103" t="s">
         <v>236</v>
-      </c>
-      <c r="C103" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
@@ -2875,10 +2875,10 @@
         <v>5139</v>
       </c>
       <c r="B104" t="s">
+        <v>258</v>
+      </c>
+      <c r="C104" t="s">
         <v>259</v>
-      </c>
-      <c r="C104" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
@@ -2886,10 +2886,10 @@
         <v>5144</v>
       </c>
       <c r="B105" t="s">
+        <v>280</v>
+      </c>
+      <c r="C105" t="s">
         <v>281</v>
-      </c>
-      <c r="C105" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
@@ -2897,10 +2897,10 @@
         <v>5150</v>
       </c>
       <c r="B106" t="s">
+        <v>162</v>
+      </c>
+      <c r="C106" t="s">
         <v>163</v>
-      </c>
-      <c r="C106" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
@@ -2908,10 +2908,10 @@
         <v>5151</v>
       </c>
       <c r="B107" t="s">
+        <v>114</v>
+      </c>
+      <c r="C107" t="s">
         <v>115</v>
-      </c>
-      <c r="C107" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
@@ -2919,10 +2919,10 @@
         <v>5155</v>
       </c>
       <c r="B108" t="s">
+        <v>146</v>
+      </c>
+      <c r="C108" t="s">
         <v>147</v>
-      </c>
-      <c r="C108" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
@@ -2930,10 +2930,10 @@
         <v>5157</v>
       </c>
       <c r="B109" t="s">
+        <v>32</v>
+      </c>
+      <c r="C109" t="s">
         <v>33</v>
-      </c>
-      <c r="C109" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
@@ -2941,10 +2941,10 @@
         <v>5160</v>
       </c>
       <c r="B110" t="s">
+        <v>56</v>
+      </c>
+      <c r="C110" t="s">
         <v>57</v>
-      </c>
-      <c r="C110" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
@@ -2952,10 +2952,10 @@
         <v>5167</v>
       </c>
       <c r="B111" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" t="s">
         <v>269</v>
-      </c>
-      <c r="C111" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
@@ -2963,10 +2963,10 @@
         <v>5170</v>
       </c>
       <c r="B112" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" t="s">
         <v>23</v>
-      </c>
-      <c r="C112" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
@@ -2974,10 +2974,10 @@
         <v>5175</v>
       </c>
       <c r="B113" t="s">
+        <v>92</v>
+      </c>
+      <c r="C113" t="s">
         <v>93</v>
-      </c>
-      <c r="C113" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
@@ -2985,10 +2985,10 @@
         <v>5176</v>
       </c>
       <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="s">
         <v>17</v>
-      </c>
-      <c r="C114" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
@@ -2996,10 +2996,10 @@
         <v>5177</v>
       </c>
       <c r="B115" t="s">
+        <v>178</v>
+      </c>
+      <c r="C115" t="s">
         <v>179</v>
-      </c>
-      <c r="C115" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
@@ -3007,10 +3007,10 @@
         <v>5181</v>
       </c>
       <c r="B116" t="s">
+        <v>208</v>
+      </c>
+      <c r="C116" t="s">
         <v>209</v>
-      </c>
-      <c r="C116" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
@@ -3018,10 +3018,10 @@
         <v>5182</v>
       </c>
       <c r="B117" t="s">
+        <v>70</v>
+      </c>
+      <c r="C117" t="s">
         <v>71</v>
-      </c>
-      <c r="C117" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
@@ -3029,10 +3029,10 @@
         <v>5197</v>
       </c>
       <c r="B118" t="s">
+        <v>136</v>
+      </c>
+      <c r="C118" t="s">
         <v>137</v>
-      </c>
-      <c r="C118" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
@@ -3040,10 +3040,10 @@
         <v>5201</v>
       </c>
       <c r="B119" t="s">
+        <v>228</v>
+      </c>
+      <c r="C119" t="s">
         <v>229</v>
-      </c>
-      <c r="C119" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
@@ -3051,10 +3051,10 @@
         <v>5203</v>
       </c>
       <c r="B120" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" t="s">
         <v>243</v>
-      </c>
-      <c r="C120" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
@@ -3062,10 +3062,10 @@
         <v>5204</v>
       </c>
       <c r="B121" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121" t="s">
         <v>123</v>
-      </c>
-      <c r="C121" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
@@ -3073,10 +3073,10 @@
         <v>5208</v>
       </c>
       <c r="B122" t="s">
+        <v>244</v>
+      </c>
+      <c r="C122" t="s">
         <v>245</v>
-      </c>
-      <c r="C122" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
@@ -3084,10 +3084,10 @@
         <v>5218</v>
       </c>
       <c r="B123" t="s">
+        <v>278</v>
+      </c>
+      <c r="C123" t="s">
         <v>279</v>
-      </c>
-      <c r="C123" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
@@ -3095,10 +3095,10 @@
         <v>5224</v>
       </c>
       <c r="B124" t="s">
+        <v>52</v>
+      </c>
+      <c r="C124" t="s">
         <v>53</v>
-      </c>
-      <c r="C124" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
@@ -3106,10 +3106,10 @@
         <v>5225</v>
       </c>
       <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
         <v>27</v>
-      </c>
-      <c r="C125" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
@@ -3117,10 +3117,10 @@
         <v>5227</v>
       </c>
       <c r="B126" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" t="s">
         <v>181</v>
-      </c>
-      <c r="C126" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
@@ -3128,10 +3128,10 @@
         <v>5232</v>
       </c>
       <c r="B127" t="s">
+        <v>272</v>
+      </c>
+      <c r="C127" t="s">
         <v>273</v>
-      </c>
-      <c r="C127" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
@@ -3139,10 +3139,10 @@
         <v>5235</v>
       </c>
       <c r="B128" t="s">
+        <v>28</v>
+      </c>
+      <c r="C128" t="s">
         <v>29</v>
-      </c>
-      <c r="C128" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
@@ -3150,10 +3150,10 @@
         <v>5236</v>
       </c>
       <c r="B129" t="s">
+        <v>120</v>
+      </c>
+      <c r="C129" t="s">
         <v>121</v>
-      </c>
-      <c r="C129" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
@@ -3161,10 +3161,10 @@
         <v>5238</v>
       </c>
       <c r="B130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C130" t="s">
         <v>109</v>
-      </c>
-      <c r="C130" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
@@ -3172,10 +3172,10 @@
         <v>5239</v>
       </c>
       <c r="B131" t="s">
+        <v>152</v>
+      </c>
+      <c r="C131" t="s">
         <v>153</v>
-      </c>
-      <c r="C131" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -3183,10 +3183,10 @@
         <v>5242</v>
       </c>
       <c r="B132" t="s">
+        <v>308</v>
+      </c>
+      <c r="C132" t="s">
         <v>309</v>
-      </c>
-      <c r="C132" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
@@ -3194,10 +3194,10 @@
         <v>5247</v>
       </c>
       <c r="B133" t="s">
+        <v>72</v>
+      </c>
+      <c r="C133" t="s">
         <v>73</v>
-      </c>
-      <c r="C133" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
@@ -3205,10 +3205,10 @@
         <v>5251</v>
       </c>
       <c r="B134" t="s">
+        <v>182</v>
+      </c>
+      <c r="C134" t="s">
         <v>183</v>
-      </c>
-      <c r="C134" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
@@ -3216,10 +3216,10 @@
         <v>5252</v>
       </c>
       <c r="B135" t="s">
+        <v>252</v>
+      </c>
+      <c r="C135" t="s">
         <v>253</v>
-      </c>
-      <c r="C135" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
@@ -3227,10 +3227,10 @@
         <v>5254</v>
       </c>
       <c r="B136" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C136" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
@@ -3238,10 +3238,10 @@
         <v>5255</v>
       </c>
       <c r="B137" t="s">
+        <v>84</v>
+      </c>
+      <c r="C137" t="s">
         <v>85</v>
-      </c>
-      <c r="C137" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
@@ -3249,10 +3249,10 @@
         <v>5256</v>
       </c>
       <c r="B138" t="s">
+        <v>290</v>
+      </c>
+      <c r="C138" t="s">
         <v>291</v>
-      </c>
-      <c r="C138" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
@@ -3260,10 +3260,10 @@
         <v>5257</v>
       </c>
       <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
         <v>11</v>
-      </c>
-      <c r="C139" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
@@ -3271,10 +3271,10 @@
         <v>5259</v>
       </c>
       <c r="B140" t="s">
+        <v>142</v>
+      </c>
+      <c r="C140" t="s">
         <v>143</v>
-      </c>
-      <c r="C140" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
@@ -3282,10 +3282,10 @@
         <v>5260</v>
       </c>
       <c r="B141" t="s">
+        <v>58</v>
+      </c>
+      <c r="C141" t="s">
         <v>59</v>
-      </c>
-      <c r="C141" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
@@ -3293,10 +3293,10 @@
         <v>5262</v>
       </c>
       <c r="B142" t="s">
+        <v>88</v>
+      </c>
+      <c r="C142" t="s">
         <v>89</v>
-      </c>
-      <c r="C142" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
@@ -3304,10 +3304,10 @@
         <v>5263</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C143" t="s">
         <v>311</v>
-      </c>
-      <c r="C143" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
@@ -3315,10 +3315,10 @@
         <v>5265</v>
       </c>
       <c r="B144" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" t="s">
         <v>173</v>
-      </c>
-      <c r="C144" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
@@ -3326,10 +3326,10 @@
         <v>5266</v>
       </c>
       <c r="B145" t="s">
+        <v>102</v>
+      </c>
+      <c r="C145" t="s">
         <v>103</v>
-      </c>
-      <c r="C145" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
@@ -3337,10 +3337,10 @@
         <v>5268</v>
       </c>
       <c r="B146" t="s">
+        <v>190</v>
+      </c>
+      <c r="C146" t="s">
         <v>191</v>
-      </c>
-      <c r="C146" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -3348,10 +3348,10 @@
         <v>5272</v>
       </c>
       <c r="B147" t="s">
+        <v>50</v>
+      </c>
+      <c r="C147" t="s">
         <v>51</v>
-      </c>
-      <c r="C147" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
@@ -3359,10 +3359,10 @@
         <v>5273</v>
       </c>
       <c r="B148" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148" t="s">
         <v>149</v>
-      </c>
-      <c r="C148" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
@@ -3370,10 +3370,10 @@
         <v>5274</v>
       </c>
       <c r="B149" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" t="s">
         <v>45</v>
-      </c>
-      <c r="C149" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
@@ -3381,10 +3381,10 @@
         <v>5275</v>
       </c>
       <c r="B150" t="s">
+        <v>204</v>
+      </c>
+      <c r="C150" t="s">
         <v>205</v>
-      </c>
-      <c r="C150" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
@@ -3392,10 +3392,10 @@
         <v>5277</v>
       </c>
       <c r="B151" t="s">
+        <v>233</v>
+      </c>
+      <c r="C151" t="s">
         <v>234</v>
-      </c>
-      <c r="C151" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
@@ -3403,10 +3403,10 @@
         <v>5278</v>
       </c>
       <c r="B152" t="s">
+        <v>128</v>
+      </c>
+      <c r="C152" t="s">
         <v>129</v>
-      </c>
-      <c r="C152" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -3414,10 +3414,10 @@
         <v>5279</v>
       </c>
       <c r="B153" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
@@ -3425,10 +3425,10 @@
         <v>5280</v>
       </c>
       <c r="B154" t="s">
+        <v>288</v>
+      </c>
+      <c r="C154" t="s">
         <v>289</v>
-      </c>
-      <c r="C154" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
@@ -3436,10 +3436,10 @@
         <v>5281</v>
       </c>
       <c r="B155" t="s">
+        <v>30</v>
+      </c>
+      <c r="C155" t="s">
         <v>31</v>
-      </c>
-      <c r="C155" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
@@ -3447,10 +3447,10 @@
         <v>5282</v>
       </c>
       <c r="B156" t="s">
+        <v>306</v>
+      </c>
+      <c r="C156" t="s">
         <v>307</v>
-      </c>
-      <c r="C156" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
@@ -3458,10 +3458,10 @@
         <v>5284</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" t="s">
         <v>313</v>
-      </c>
-      <c r="C157" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
@@ -3469,10 +3469,10 @@
         <v>5286</v>
       </c>
       <c r="B158" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C158" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
@@ -3480,10 +3480,10 @@
         <v>5287</v>
       </c>
       <c r="B159" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
@@ -3491,10 +3491,10 @@
         <v>5288</v>
       </c>
       <c r="B160" t="s">
+        <v>231</v>
+      </c>
+      <c r="C160" t="s">
         <v>232</v>
-      </c>
-      <c r="C160" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
@@ -3502,10 +3502,10 @@
         <v>5289</v>
       </c>
       <c r="B161" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C161" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.4">
@@ -3513,10 +3513,10 @@
         <v>5290</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C162" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.4">
@@ -3524,10 +3524,10 @@
         <v>5292</v>
       </c>
       <c r="B163" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C163" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.4">
@@ -3535,10 +3535,10 @@
         <v>5293</v>
       </c>
       <c r="B164" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C164" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.4">
@@ -3546,10 +3546,10 @@
         <v>5283</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C165" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.4">
@@ -3557,10 +3557,10 @@
         <v>5301</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166" t="s">
         <v>329</v>
-      </c>
-      <c r="C166" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.4">
@@ -3568,10 +3568,10 @@
         <v>5302</v>
       </c>
       <c r="B167" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C167" t="s">
         <v>331</v>
-      </c>
-      <c r="C167" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.4">
@@ -3579,10 +3579,10 @@
         <v>5303</v>
       </c>
       <c r="B168" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C168" t="s">
         <v>333</v>
-      </c>
-      <c r="C168" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.4">
@@ -3590,10 +3590,10 @@
         <v>5298</v>
       </c>
       <c r="B169" t="s">
+        <v>334</v>
+      </c>
+      <c r="C169" t="s">
         <v>335</v>
-      </c>
-      <c r="C169" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.4">
@@ -3601,10 +3601,10 @@
         <v>5295</v>
       </c>
       <c r="B170" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C170" t="s">
         <v>337</v>
-      </c>
-      <c r="C170" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.4">
@@ -3612,10 +3612,10 @@
         <v>5311</v>
       </c>
       <c r="B171" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" t="s">
         <v>341</v>
-      </c>
-      <c r="C171" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.4">
@@ -3623,10 +3623,10 @@
         <v>5317</v>
       </c>
       <c r="B172" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C172" t="s">
         <v>343</v>
-      </c>
-      <c r="C172" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.4">
@@ -3634,10 +3634,10 @@
         <v>5306</v>
       </c>
       <c r="B173" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" t="s">
         <v>345</v>
-      </c>
-      <c r="C173" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.4">
@@ -3645,10 +3645,10 @@
         <v>5323</v>
       </c>
       <c r="B174" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C174" t="s">
         <v>347</v>
-      </c>
-      <c r="C174" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.4">
@@ -3656,10 +3656,10 @@
         <v>5322</v>
       </c>
       <c r="B175" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C175" t="s">
         <v>349</v>
-      </c>
-      <c r="C175" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.4">
@@ -3667,10 +3667,10 @@
         <v>5315</v>
       </c>
       <c r="B176" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" t="s">
         <v>351</v>
-      </c>
-      <c r="C176" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.4">
@@ -3678,10 +3678,10 @@
         <v>5310</v>
       </c>
       <c r="B177" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" t="s">
         <v>353</v>
-      </c>
-      <c r="C177" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.4">
@@ -3689,10 +3689,10 @@
         <v>5325</v>
       </c>
       <c r="B178" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C178" t="s">
         <v>355</v>
-      </c>
-      <c r="C178" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.4">
@@ -3700,10 +3700,10 @@
         <v>5326</v>
       </c>
       <c r="B179" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" t="s">
         <v>357</v>
-      </c>
-      <c r="C179" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.4">
@@ -3711,10 +3711,10 @@
         <v>5324</v>
       </c>
       <c r="B180" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" t="s">
         <v>359</v>
-      </c>
-      <c r="C180" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.4">
@@ -3722,10 +3722,10 @@
         <v>5328</v>
       </c>
       <c r="B181" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" t="s">
         <v>361</v>
-      </c>
-      <c r="C181" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.4">
@@ -3733,10 +3733,10 @@
         <v>5327</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C182" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.4">
@@ -3744,10 +3744,10 @@
         <v>5329</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" t="s">
         <v>365</v>
-      </c>
-      <c r="C183" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.4">
@@ -3755,10 +3755,10 @@
         <v>5334</v>
       </c>
       <c r="B184" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" t="s">
         <v>367</v>
-      </c>
-      <c r="C184" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.4">
@@ -3766,10 +3766,10 @@
         <v>5330</v>
       </c>
       <c r="B185" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C185" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.4">
@@ -3777,10 +3777,10 @@
         <v>5333</v>
       </c>
       <c r="B186" t="s">
+        <v>369</v>
+      </c>
+      <c r="C186" t="s">
         <v>370</v>
-      </c>
-      <c r="C186" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.4">
@@ -3788,10 +3788,10 @@
         <v>5335</v>
       </c>
       <c r="B187" t="s">
+        <v>372</v>
+      </c>
+      <c r="C187" t="s">
         <v>373</v>
-      </c>
-      <c r="C187" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.4">
@@ -3799,10 +3799,10 @@
         <v>5338</v>
       </c>
       <c r="B188" t="s">
+        <v>374</v>
+      </c>
+      <c r="C188" t="s">
         <v>375</v>
-      </c>
-      <c r="C188" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.4">
@@ -3810,10 +3810,10 @@
         <v>5304</v>
       </c>
       <c r="B189" t="s">
+        <v>376</v>
+      </c>
+      <c r="C189" t="s">
         <v>377</v>
-      </c>
-      <c r="C189" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.4">
@@ -3821,10 +3821,10 @@
         <v>5307</v>
       </c>
       <c r="B190" t="s">
+        <v>378</v>
+      </c>
+      <c r="C190" t="s">
         <v>379</v>
-      </c>
-      <c r="C190" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.4">
@@ -3832,10 +3832,10 @@
         <v>5332</v>
       </c>
       <c r="B191" t="s">
+        <v>380</v>
+      </c>
+      <c r="C191" t="s">
         <v>381</v>
-      </c>
-      <c r="C191" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.4">
@@ -3843,10 +3843,10 @@
         <v>5297</v>
       </c>
       <c r="B192" t="s">
+        <v>382</v>
+      </c>
+      <c r="C192" t="s">
         <v>383</v>
-      </c>
-      <c r="C192" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.4">
@@ -3854,10 +3854,10 @@
         <v>5314</v>
       </c>
       <c r="B193" t="s">
+        <v>384</v>
+      </c>
+      <c r="C193" t="s">
         <v>385</v>
-      </c>
-      <c r="C193" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.4">
@@ -3865,10 +3865,10 @@
         <v>5337</v>
       </c>
       <c r="B194" t="s">
+        <v>386</v>
+      </c>
+      <c r="C194" t="s">
         <v>387</v>
-      </c>
-      <c r="C194" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.4">
@@ -3876,10 +3876,10 @@
         <v>5308</v>
       </c>
       <c r="B195" t="s">
+        <v>388</v>
+      </c>
+      <c r="C195" t="s">
         <v>389</v>
-      </c>
-      <c r="C195" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.4">
@@ -3887,10 +3887,10 @@
         <v>5305</v>
       </c>
       <c r="B196" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" t="s">
         <v>391</v>
-      </c>
-      <c r="C196" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.4">
@@ -3898,10 +3898,10 @@
         <v>5336</v>
       </c>
       <c r="B197" t="s">
+        <v>392</v>
+      </c>
+      <c r="C197" t="s">
         <v>393</v>
-      </c>
-      <c r="C197" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.4">
@@ -3909,10 +3909,10 @@
         <v>5319</v>
       </c>
       <c r="B198" t="s">
+        <v>394</v>
+      </c>
+      <c r="C198" t="s">
         <v>395</v>
-      </c>
-      <c r="C198" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.4">
@@ -3920,10 +3920,10 @@
         <v>5341</v>
       </c>
       <c r="B199" t="s">
+        <v>396</v>
+      </c>
+      <c r="C199" t="s">
         <v>397</v>
-      </c>
-      <c r="C199" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.4">
@@ -3931,10 +3931,10 @@
         <v>5342</v>
       </c>
       <c r="B200" t="s">
+        <v>398</v>
+      </c>
+      <c r="C200" t="s">
         <v>399</v>
-      </c>
-      <c r="C200" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.4">
@@ -3942,10 +3942,10 @@
         <v>5343</v>
       </c>
       <c r="B201" t="s">
+        <v>400</v>
+      </c>
+      <c r="C201" t="s">
         <v>401</v>
-      </c>
-      <c r="C201" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="217" spans="6:6" x14ac:dyDescent="0.4">

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4831BCE9-2692-4E43-BB9B-412E418821ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D028269B-8234-4352-9BAC-ABA422276AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23543" yWindow="180" windowWidth="18517" windowHeight="10740" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{A5566D1E-FB50-4646-A727-6AF21217A2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -1247,7 +1247,7 @@
     <t>c5d0c01d-3717-4dba-bf51-652813b22c8c</t>
   </si>
   <si>
-    <t>stakeholderid</t>
+    <t>Coluna2</t>
   </si>
 </sst>
 </file>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F525BC-1C09-441C-915A-B63D91F42BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="403">
   <si>
     <t>matricula</t>
   </si>
@@ -1228,8 +1234,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1292,13 +1298,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1336,7 +1350,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1370,6 +1384,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1404,9 +1419,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1579,11 +1595,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C202"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1605,7 +1624,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>224</v>
       </c>
@@ -1616,7 +1635,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>236</v>
       </c>
@@ -1627,7 +1646,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1221</v>
       </c>
@@ -1638,7 +1657,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1464</v>
       </c>
@@ -1649,7 +1668,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1499</v>
       </c>
@@ -1660,7 +1679,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2063</v>
       </c>
@@ -1671,7 +1690,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2086</v>
       </c>
@@ -1682,7 +1701,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>2638</v>
       </c>
@@ -1693,7 +1712,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2916</v>
       </c>
@@ -1704,7 +1723,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>3014</v>
       </c>
@@ -1715,7 +1734,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>3230</v>
       </c>
@@ -1726,7 +1745,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>3358</v>
       </c>
@@ -1737,7 +1756,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>3435</v>
       </c>
@@ -1748,7 +1767,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>3528</v>
       </c>
@@ -1759,7 +1778,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>3688</v>
       </c>
@@ -1770,7 +1789,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>3709</v>
       </c>
@@ -1781,7 +1800,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3727</v>
       </c>
@@ -1792,7 +1811,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3729</v>
       </c>
@@ -1803,7 +1822,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3811</v>
       </c>
@@ -1814,7 +1833,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3874</v>
       </c>
@@ -1825,7 +1844,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3908</v>
       </c>
@@ -1836,7 +1855,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3951</v>
       </c>
@@ -1847,7 +1866,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>4007</v>
       </c>
@@ -1858,7 +1877,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>4031</v>
       </c>
@@ -1869,7 +1888,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>4039</v>
       </c>
@@ -1880,7 +1899,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>4111</v>
       </c>
@@ -1891,7 +1910,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>4262</v>
       </c>
@@ -1902,7 +1921,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>4300</v>
       </c>
@@ -1913,7 +1932,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>4333</v>
       </c>
@@ -1924,7 +1943,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>4340</v>
       </c>
@@ -1935,7 +1954,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>4369</v>
       </c>
@@ -1946,7 +1965,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>4390</v>
       </c>
@@ -1957,7 +1976,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>4433</v>
       </c>
@@ -1968,7 +1987,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>4464</v>
       </c>
@@ -1979,7 +1998,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>4476</v>
       </c>
@@ -1990,7 +2009,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>4509</v>
       </c>
@@ -2001,7 +2020,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>4530</v>
       </c>
@@ -2012,7 +2031,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>4558</v>
       </c>
@@ -2023,7 +2042,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>4561</v>
       </c>
@@ -2034,7 +2053,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>4563</v>
       </c>
@@ -2045,7 +2064,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>4581</v>
       </c>
@@ -2056,7 +2075,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>4618</v>
       </c>
@@ -2067,7 +2086,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>4640</v>
       </c>
@@ -2078,7 +2097,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>4668</v>
       </c>
@@ -2089,7 +2108,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>4683</v>
       </c>
@@ -2100,7 +2119,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>4703</v>
       </c>
@@ -2111,7 +2130,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>4734</v>
       </c>
@@ -2122,7 +2141,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>4739</v>
       </c>
@@ -2133,7 +2152,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>4751</v>
       </c>
@@ -2144,7 +2163,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>4752</v>
       </c>
@@ -2155,7 +2174,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>4794</v>
       </c>
@@ -2166,7 +2185,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>4806</v>
       </c>
@@ -2177,7 +2196,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>4816</v>
       </c>
@@ -2188,7 +2207,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>4820</v>
       </c>
@@ -2199,7 +2218,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>4837</v>
       </c>
@@ -2210,7 +2229,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4838</v>
       </c>
@@ -2221,7 +2240,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4841</v>
       </c>
@@ -2232,7 +2251,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4858</v>
       </c>
@@ -2243,7 +2262,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4861</v>
       </c>
@@ -2254,7 +2273,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4863</v>
       </c>
@@ -2265,7 +2284,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4886</v>
       </c>
@@ -2276,7 +2295,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4895</v>
       </c>
@@ -2287,7 +2306,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4896</v>
       </c>
@@ -2298,7 +2317,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4902</v>
       </c>
@@ -2309,7 +2328,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4904</v>
       </c>
@@ -2320,7 +2339,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>4906</v>
       </c>
@@ -2331,7 +2350,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>4908</v>
       </c>
@@ -2342,7 +2361,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>4925</v>
       </c>
@@ -2353,7 +2372,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>4935</v>
       </c>
@@ -2364,7 +2383,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>4945</v>
       </c>
@@ -2375,7 +2394,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>4950</v>
       </c>
@@ -2386,7 +2405,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>4957</v>
       </c>
@@ -2397,7 +2416,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>4972</v>
       </c>
@@ -2408,7 +2427,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>4981</v>
       </c>
@@ -2419,7 +2438,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>4994</v>
       </c>
@@ -2430,7 +2449,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>5008</v>
       </c>
@@ -2441,7 +2460,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>5019</v>
       </c>
@@ -2452,7 +2471,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>5028</v>
       </c>
@@ -2463,7 +2482,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>5038</v>
       </c>
@@ -2474,7 +2493,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>5043</v>
       </c>
@@ -2485,7 +2504,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>5046</v>
       </c>
@@ -2496,7 +2515,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>5051</v>
       </c>
@@ -2507,7 +2526,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>5054</v>
       </c>
@@ -2518,7 +2537,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>5055</v>
       </c>
@@ -2529,7 +2548,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>5064</v>
       </c>
@@ -2540,7 +2559,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>5078</v>
       </c>
@@ -2551,7 +2570,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>5082</v>
       </c>
@@ -2562,7 +2581,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>5084</v>
       </c>
@@ -2573,7 +2592,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>5102</v>
       </c>
@@ -2584,7 +2603,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>5108</v>
       </c>
@@ -2595,7 +2614,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>5113</v>
       </c>
@@ -2606,7 +2625,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>5114</v>
       </c>
@@ -2617,7 +2636,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>5117</v>
       </c>
@@ -2628,7 +2647,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>5118</v>
       </c>
@@ -2639,7 +2658,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>5123</v>
       </c>
@@ -2650,7 +2669,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>5127</v>
       </c>
@@ -2661,7 +2680,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>5129</v>
       </c>
@@ -2672,7 +2691,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>5130</v>
       </c>
@@ -2683,7 +2702,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>5133</v>
       </c>
@@ -2694,7 +2713,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>5137</v>
       </c>
@@ -2705,7 +2724,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>5138</v>
       </c>
@@ -2716,7 +2735,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>5139</v>
       </c>
@@ -2727,7 +2746,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>5144</v>
       </c>
@@ -2738,7 +2757,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>5150</v>
       </c>
@@ -2749,7 +2768,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>5151</v>
       </c>
@@ -2760,7 +2779,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>5155</v>
       </c>
@@ -2771,7 +2790,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>5157</v>
       </c>
@@ -2782,7 +2801,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>5160</v>
       </c>
@@ -2793,7 +2812,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>5167</v>
       </c>
@@ -2804,7 +2823,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>5170</v>
       </c>
@@ -2815,7 +2834,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>5175</v>
       </c>
@@ -2826,7 +2845,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>5176</v>
       </c>
@@ -2837,7 +2856,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>5177</v>
       </c>
@@ -2848,7 +2867,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>5181</v>
       </c>
@@ -2859,7 +2878,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>5182</v>
       </c>
@@ -2870,7 +2889,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>5197</v>
       </c>
@@ -2881,7 +2900,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>5201</v>
       </c>
@@ -2892,7 +2911,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>5203</v>
       </c>
@@ -2903,7 +2922,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>5204</v>
       </c>
@@ -2914,7 +2933,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>5208</v>
       </c>
@@ -2925,7 +2944,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>5218</v>
       </c>
@@ -2936,7 +2955,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>5224</v>
       </c>
@@ -2947,7 +2966,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>5225</v>
       </c>
@@ -2958,7 +2977,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>5227</v>
       </c>
@@ -2969,7 +2988,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>5232</v>
       </c>
@@ -2980,7 +2999,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>5235</v>
       </c>
@@ -2991,7 +3010,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>5236</v>
       </c>
@@ -3002,7 +3021,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>5238</v>
       </c>
@@ -3013,7 +3032,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>5239</v>
       </c>
@@ -3024,7 +3043,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>5242</v>
       </c>
@@ -3035,7 +3054,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>5247</v>
       </c>
@@ -3046,7 +3065,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>5251</v>
       </c>
@@ -3057,7 +3076,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>5252</v>
       </c>
@@ -3068,7 +3087,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>5254</v>
       </c>
@@ -3079,7 +3098,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>5255</v>
       </c>
@@ -3090,7 +3109,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>5256</v>
       </c>
@@ -3101,7 +3120,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>5257</v>
       </c>
@@ -3112,7 +3131,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>5259</v>
       </c>
@@ -3123,7 +3142,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>5260</v>
       </c>
@@ -3134,7 +3153,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>5262</v>
       </c>
@@ -3145,7 +3164,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>5263</v>
       </c>
@@ -3156,7 +3175,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>5265</v>
       </c>
@@ -3167,7 +3186,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>5266</v>
       </c>
@@ -3178,7 +3197,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>5268</v>
       </c>
@@ -3189,7 +3208,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>5272</v>
       </c>
@@ -3200,7 +3219,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>5273</v>
       </c>
@@ -3211,7 +3230,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>5274</v>
       </c>
@@ -3222,7 +3241,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>5275</v>
       </c>
@@ -3233,7 +3252,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>5277</v>
       </c>
@@ -3244,7 +3263,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>5278</v>
       </c>
@@ -3255,7 +3274,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>5279</v>
       </c>
@@ -3266,7 +3285,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>5280</v>
       </c>
@@ -3277,7 +3296,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>5281</v>
       </c>
@@ -3288,7 +3307,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>5282</v>
       </c>
@@ -3299,7 +3318,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>5284</v>
       </c>
@@ -3310,7 +3329,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>5286</v>
       </c>
@@ -3321,7 +3340,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>5287</v>
       </c>
@@ -3332,7 +3351,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>5288</v>
       </c>
@@ -3343,7 +3362,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>5289</v>
       </c>
@@ -3354,7 +3373,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>5290</v>
       </c>
@@ -3365,7 +3384,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>5292</v>
       </c>
@@ -3376,7 +3395,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>5293</v>
       </c>
@@ -3387,7 +3406,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>5283</v>
       </c>
@@ -3398,7 +3417,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>5301</v>
       </c>
@@ -3409,7 +3428,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>5302</v>
       </c>
@@ -3420,7 +3439,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>5303</v>
       </c>
@@ -3431,7 +3450,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>5298</v>
       </c>
@@ -3442,7 +3461,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>5295</v>
       </c>
@@ -3453,7 +3472,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>5311</v>
       </c>
@@ -3464,7 +3483,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>5317</v>
       </c>
@@ -3475,7 +3494,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>5306</v>
       </c>
@@ -3486,7 +3505,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>5323</v>
       </c>
@@ -3497,7 +3516,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>5322</v>
       </c>
@@ -3508,7 +3527,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>5315</v>
       </c>
@@ -3519,7 +3538,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>5310</v>
       </c>
@@ -3530,7 +3549,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>5325</v>
       </c>
@@ -3541,7 +3560,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>5326</v>
       </c>
@@ -3552,7 +3571,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>5324</v>
       </c>
@@ -3563,7 +3582,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>5328</v>
       </c>
@@ -3574,7 +3593,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>5327</v>
       </c>
@@ -3585,7 +3604,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>5329</v>
       </c>
@@ -3596,7 +3615,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>5334</v>
       </c>
@@ -3607,7 +3626,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>5330</v>
       </c>
@@ -3618,7 +3637,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>5333</v>
       </c>
@@ -3629,7 +3648,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>5335</v>
       </c>
@@ -3640,7 +3659,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A188">
         <v>5338</v>
       </c>
@@ -3651,7 +3670,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A189">
         <v>5304</v>
       </c>
@@ -3662,7 +3681,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A190">
         <v>5307</v>
       </c>
@@ -3673,7 +3692,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A191">
         <v>5332</v>
       </c>
@@ -3684,7 +3703,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A192">
         <v>5297</v>
       </c>
@@ -3695,7 +3714,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A193">
         <v>5314</v>
       </c>
@@ -3706,7 +3725,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A194">
         <v>5337</v>
       </c>
@@ -3717,7 +3736,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A195">
         <v>5308</v>
       </c>
@@ -3728,7 +3747,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A196">
         <v>5305</v>
       </c>
@@ -3739,7 +3758,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A197">
         <v>5336</v>
       </c>
@@ -3750,7 +3769,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A198">
         <v>5319</v>
       </c>
@@ -3761,7 +3780,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A199">
         <v>5341</v>
       </c>
@@ -3772,7 +3791,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A200">
         <v>5342</v>
       </c>
@@ -3783,7 +3802,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A201">
         <v>5343</v>
       </c>
@@ -3792,6 +3811,17 @@
       </c>
       <c r="C201" t="s">
         <v>402</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A202">
+        <v>5344</v>
+      </c>
+      <c r="B202" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F525BC-1C09-441C-915A-B63D91F42BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C1C03C-72A2-4471-A164-2D7E4BADA0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21503" yWindow="-98" windowWidth="19394" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="413">
   <si>
     <t>matricula</t>
   </si>
@@ -1229,6 +1229,36 @@
   </si>
   <si>
     <t>c5d0c01d-3717-4dba-bf51-652813b22c8c</t>
+  </si>
+  <si>
+    <t>CAROLINA MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>d87ba166-e6e2-411d-b53f-e91ebfe0b28b</t>
+  </si>
+  <si>
+    <t>DEUSINARA MENDES CORREA</t>
+  </si>
+  <si>
+    <t>7c12fc30-5e26-4b15-9cca-b8f164433595</t>
+  </si>
+  <si>
+    <t>MARIA GILVANIR DA SILVA</t>
+  </si>
+  <si>
+    <t>eae5079f-1fbf-4d7c-b963-a0b578994d5c</t>
+  </si>
+  <si>
+    <t>MARIA VIVIANE DOS SANTOS SOARES</t>
+  </si>
+  <si>
+    <t>RENATA GUERRA MARCELINO</t>
+  </si>
+  <si>
+    <t>50a22877-50ea-472e-937e-d23234e321c9</t>
+  </si>
+  <si>
+    <t>efc43d56-5179-4451-af49-81c60b41c688</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C207"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -3824,7 +3854,63 @@
         <v>393</v>
       </c>
     </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A203">
+        <v>5345</v>
+      </c>
+      <c r="B203" t="s">
+        <v>409</v>
+      </c>
+      <c r="C203" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A204">
+        <v>5347</v>
+      </c>
+      <c r="B204" t="s">
+        <v>410</v>
+      </c>
+      <c r="C204" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A205">
+        <v>5348</v>
+      </c>
+      <c r="B205" t="s">
+        <v>403</v>
+      </c>
+      <c r="C205" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A206">
+        <v>5350</v>
+      </c>
+      <c r="B206" t="s">
+        <v>405</v>
+      </c>
+      <c r="C206" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A207">
+        <v>5353</v>
+      </c>
+      <c r="B207" t="s">
+        <v>407</v>
+      </c>
+      <c r="C207" t="s">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C1C03C-72A2-4471-A164-2D7E4BADA0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D34F57-B4D8-4DF8-A725-C665D22485F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21503" yWindow="-98" windowWidth="19394" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="419">
   <si>
     <t>matricula</t>
   </si>
@@ -1259,6 +1259,24 @@
   </si>
   <si>
     <t>efc43d56-5179-4451-af49-81c60b41c688</t>
+  </si>
+  <si>
+    <t>JESSICA CRISTINA XAVIER</t>
+  </si>
+  <si>
+    <t>c6a104ce-8bf6-43a3-884d-76fd415fa203</t>
+  </si>
+  <si>
+    <t>MARILIA KELIA ALVES DE ARAUJO SILVA</t>
+  </si>
+  <si>
+    <t>00cc10cf-bb30-439f-82c1-c7b7647af048</t>
+  </si>
+  <si>
+    <t>VIVIANE MARIA DA SILVA</t>
+  </si>
+  <si>
+    <t>9e53601a-b77c-4989-bf38-457e6a6f2945</t>
   </si>
 </sst>
 </file>
@@ -1317,11 +1335,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1626,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C207"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -3909,6 +3928,39 @@
         <v>408</v>
       </c>
     </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A208">
+        <v>5357</v>
+      </c>
+      <c r="B208" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A209">
+        <v>5358</v>
+      </c>
+      <c r="B209" t="s">
+        <v>415</v>
+      </c>
+      <c r="C209" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A210">
+        <v>5356</v>
+      </c>
+      <c r="B210" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D34F57-B4D8-4DF8-A725-C665D22485F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47F48CB-0301-41DF-BD38-DD11E600C109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="429">
   <si>
     <t>matricula</t>
   </si>
@@ -1277,6 +1277,36 @@
   </si>
   <si>
     <t>9e53601a-b77c-4989-bf38-457e6a6f2945</t>
+  </si>
+  <si>
+    <t>BRENDA JOYCE FORTUNATO SANTOS</t>
+  </si>
+  <si>
+    <t>f890b1eb-e2ee-45f4-bf60-0c1e80a0bd93</t>
+  </si>
+  <si>
+    <t>LUANDRA RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>a0d8c904-e5de-41aa-838e-64d32de3b6d3</t>
+  </si>
+  <si>
+    <t>MEIRE CRISTINA MACHADO FRANCO</t>
+  </si>
+  <si>
+    <t>43c9a33b-5afd-4537-ba88-786c54fb2882</t>
+  </si>
+  <si>
+    <t>REJANE VIRGENS DE JESUS</t>
+  </si>
+  <si>
+    <t>b2069e5a-2aa9-4f23-80bb-8985f0df8b69</t>
+  </si>
+  <si>
+    <t>ELIZABETE DIAS</t>
+  </si>
+  <si>
+    <t>718486bb-d598-41cb-ab52-020b8e701b36</t>
   </si>
 </sst>
 </file>
@@ -1645,10 +1675,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C210"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -3961,6 +3992,72 @@
         <v>418</v>
       </c>
     </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A211">
+        <v>5346</v>
+      </c>
+      <c r="B211" t="s">
+        <v>419</v>
+      </c>
+      <c r="C211" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A212">
+        <v>5339</v>
+      </c>
+      <c r="B212" t="s">
+        <v>143</v>
+      </c>
+      <c r="C212" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A213">
+        <v>5351</v>
+      </c>
+      <c r="B213" t="s">
+        <v>421</v>
+      </c>
+      <c r="C213" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A214">
+        <v>5355</v>
+      </c>
+      <c r="B214" t="s">
+        <v>423</v>
+      </c>
+      <c r="C214" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A215">
+        <v>5352</v>
+      </c>
+      <c r="B215" t="s">
+        <v>425</v>
+      </c>
+      <c r="C215" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A216">
+        <v>5349</v>
+      </c>
+      <c r="B216" t="s">
+        <v>427</v>
+      </c>
+      <c r="C216" t="s">
+        <v>428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47F48CB-0301-41DF-BD38-DD11E600C109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998D9285-015F-4469-BFF7-97EFAAF996CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="429">
   <si>
     <t>matricula</t>
   </si>
@@ -1365,12 +1365,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1675,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4058,6 +4061,17 @@
         <v>428</v>
       </c>
     </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A217">
+        <v>5364</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C217" t="s">
+        <v>422</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998D9285-015F-4469-BFF7-97EFAAF996CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50D29D5-D841-4FD8-8D1E-25FA3B9D35CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50D29D5-D841-4FD8-8D1E-25FA3B9D35CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA4AF44-DAB9-47EC-8979-81962127ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="433">
   <si>
     <t>matricula</t>
   </si>
@@ -1307,6 +1307,18 @@
   </si>
   <si>
     <t>718486bb-d598-41cb-ab52-020b8e701b36</t>
+  </si>
+  <si>
+    <t>SIRLEI CORDEIRO FERREIRA</t>
+  </si>
+  <si>
+    <t>5d7ac0a4-54a3-40a3-a72c-043edc6095c8</t>
+  </si>
+  <si>
+    <t>MARIA DO AMPARO DA SILVA</t>
+  </si>
+  <si>
+    <t>8173604d-6d2f-4816-a34b-e7b5fef7f8a7</t>
   </si>
 </sst>
 </file>
@@ -1678,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4072,6 +4084,28 @@
         <v>422</v>
       </c>
     </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A218">
+        <v>5300</v>
+      </c>
+      <c r="B218" t="s">
+        <v>429</v>
+      </c>
+      <c r="C218" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A219">
+        <v>5309</v>
+      </c>
+      <c r="B219" t="s">
+        <v>431</v>
+      </c>
+      <c r="C219" t="s">
+        <v>432</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA4AF44-DAB9-47EC-8979-81962127ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A901313-5E87-473B-9CA0-212A8E496728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="441">
   <si>
     <t>matricula</t>
   </si>
@@ -1319,13 +1319,37 @@
   </si>
   <si>
     <t>8173604d-6d2f-4816-a34b-e7b5fef7f8a7</t>
+  </si>
+  <si>
+    <t>CARLIANA RIBEIRO DA SILVA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>IVONE NOVAIS DA SILVA</t>
+  </si>
+  <si>
+    <t>f6652a46-1026-4280-a311-74ffd34c3b6d</t>
+  </si>
+  <si>
+    <t>1e1b7f59-25e3-4685-888f-96f790d83379</t>
+  </si>
+  <si>
+    <t>MARIA MADALENA CELESTINO DA SILVA TEIXEIRA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>c76e903d-b281-457d-9a89-c098f92f92e0</t>
+  </si>
+  <si>
+    <t>CLEONICE DA SILVA RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>d67b40dc-9b49-4307-a402-a2643561e4f6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1340,6 +1364,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5A5C5E"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1377,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1385,6 +1415,12 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1690,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C223"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4106,6 +4142,50 @@
         <v>432</v>
       </c>
     </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A220" s="4">
+        <v>5365</v>
+      </c>
+      <c r="B220" t="s">
+        <v>433</v>
+      </c>
+      <c r="C220" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A221" s="4">
+        <v>5366</v>
+      </c>
+      <c r="B221" t="s">
+        <v>434</v>
+      </c>
+      <c r="C221" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A222" s="4">
+        <v>5362</v>
+      </c>
+      <c r="B222" t="s">
+        <v>437</v>
+      </c>
+      <c r="C222" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A223" s="4">
+        <v>5367</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C223" t="s">
+        <v>440</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A901313-5E87-473B-9CA0-212A8E496728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3132FC-62AB-41AA-865F-D8BA7E872F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="443">
   <si>
     <t>matricula</t>
   </si>
@@ -1343,6 +1343,12 @@
   </si>
   <si>
     <t>d67b40dc-9b49-4307-a402-a2643561e4f6</t>
+  </si>
+  <si>
+    <t>ROSIMEIRE GABRIEL DA SILVA</t>
+  </si>
+  <si>
+    <t>c128a5f2-d056-48f5-8d7a-11d09d879abf</t>
   </si>
 </sst>
 </file>
@@ -1726,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C223"/>
+  <dimension ref="A1:C224"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4186,6 +4192,17 @@
         <v>440</v>
       </c>
     </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A224" s="4">
+        <v>5368</v>
+      </c>
+      <c r="B224" t="s">
+        <v>441</v>
+      </c>
+      <c r="C224" t="s">
+        <v>442</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/projeto/FUNC.xlsx
+++ b/projeto/FUNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3132FC-62AB-41AA-865F-D8BA7E872F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FA6628-7CA2-4688-88E6-2E46E7DF649E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="449">
   <si>
     <t>matricula</t>
   </si>
@@ -1349,6 +1349,24 @@
   </si>
   <si>
     <t>c128a5f2-d056-48f5-8d7a-11d09d879abf</t>
+  </si>
+  <si>
+    <t>MARCIA ELAINE SIMOES FERRO RIBEIRO</t>
+  </si>
+  <si>
+    <t>052d9747-3e95-4876-9c5f-d0e3cd1f50d5</t>
+  </si>
+  <si>
+    <t>ISADORA RIBEIRO DE SOUZA</t>
+  </si>
+  <si>
+    <t>6d984f2a-811e-497f-a39e-4fb507196201</t>
+  </si>
+  <si>
+    <t>LETICIA DE SOUZA BRAQUE FARKAS</t>
+  </si>
+  <si>
+    <t>eabc83fb-f110-472e-b134-94ba69f47022</t>
   </si>
 </sst>
 </file>
@@ -1732,7 +1750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C224"/>
+  <dimension ref="A1:C227"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.61328125" bestFit="1" customWidth="1"/>
@@ -4203,6 +4221,39 @@
         <v>442</v>
       </c>
     </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A225" s="4">
+        <v>5361</v>
+      </c>
+      <c r="B225" t="s">
+        <v>443</v>
+      </c>
+      <c r="C225" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A226" s="4">
+        <v>5370</v>
+      </c>
+      <c r="B226" t="s">
+        <v>445</v>
+      </c>
+      <c r="C226" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A227" s="4">
+        <v>5371</v>
+      </c>
+      <c r="B227" t="s">
+        <v>447</v>
+      </c>
+      <c r="C227" t="s">
+        <v>448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
